--- a/03_주제별_경혈고증_연구보고서/흉부경혈_심장막자상_고증/흉부경혈_심장막자상_문헌고증_DB.xlsx
+++ b/03_주제별_경혈고증_연구보고서/흉부경혈_심장막자상_고증/흉부경혈_심장막자상_문헌고증_DB.xlsx
@@ -11,15 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="혈위_3D기하" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보정_k임계" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명치_두측경사" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="膻中_흉골" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심장_도달부위" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자침깊이" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_루브릭" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_결과" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌_근거포인터" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PubMed_근거" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자입깊이별_도달" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="膻中_흉골" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심장_도달부위" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자침깊이" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_루브릭" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_결과" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌_근거포인터" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PubMed_근거" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.8" customWidth="1" min="1" max="1"/>
@@ -526,78 +527,90 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>침 길이 (mm)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>50</v>
+          <t>침 조건</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>침체(針身) 길이 50 mm, 손잡이(針柄) 제외 = 최대 자입 깊이 50 mm. 모든 거리는 피부점에서 침 경로를 따라 잰 자입 깊이</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>보정 계수 k_cal</t>
+          <t>최대 자입 깊이 (mm)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.699</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>보정 근거</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>papers.id 2476 (PMID 22741258) 鳩尾 직자 위험 깊이 16.99±2.86 mm ÷ BodyParts3D 같은 경로 간 24.3 mm</t>
-        </is>
+          <t>보정 계수 k_cal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>모형 한계</t>
+          <t>보정 근거</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>심장막·심외막·폐 실질 메쉬 없음(폐는 기관지·폐혈관만). 심장 거리는 심실강·유두근·관상혈관 첫 교차</t>
+          <t>papers.id 2476 (PMID 22741258) 鳩尾 직자 위험 깊이 16.99±2.86 mm ÷ BodyParts3D 같은 경로 간 24.3 mm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>좌표</t>
+          <t>모형 한계</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+X 좌측, -Y 전방, +Z 상방 (BodyParts3D 원좌표). 표의 x_mm은 정중선 기준</t>
+          <t>심장막·심외막·폐 실질 메쉬 없음(폐는 기관지·폐혈관만). 심장 거리는 심실강·유두근·관상혈관 첫 교차</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>분석 스크립트(내부)</t>
+          <t>좌표</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>scratchpad chest_geom.py / chest_extra.py / heart_part.py / chest_section.py (Möller–Trumbore 광선 교차, 원뿔 600방향)</t>
+          <t>+X 좌측, -Y 전방, +Z 상방 (BodyParts3D 원좌표). 표의 x_mm은 정중선 기준</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>분석 스크립트(내부)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>scratchpad chest_geom.py / chest_extra.py / heart_part.py / chest_section.py (Möller–Trumbore 광선 교차, 원뿔 600방향)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>BodyParts3D 원본</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>%LOCALAPPDATA%\acupoint_fma\bodyparts3d\partof_BP3D_4.0_obj_99 ; 색인 02_Master_Datasets/FMA/BodyParts3D/bp3d_fma_index.json</t>
         </is>
@@ -609,6 +622,273 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13.2" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9.9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>혈위</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ARI-Core A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ARI-Core B</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>평균 ± 반범위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>게이트</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>등가중치(평균)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>민감도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CV17</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>78.75 ± 1.25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3 ⚠</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KI23-L</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>75.0 ± 1.25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3 ⚠</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KI22-L</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="C4" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72.5 ± 1.25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3 ⚠</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>가중치 민감(C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ST18-L</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>71.25 ± 2.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3 ⚠</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CV15</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>70.0 ± 1.25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3 ⚠</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>가중치 민감(C)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -927,7 +1207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2253,7 +2533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2603,7 +2883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4496,7 +4776,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12.1" customWidth="1" min="3" max="3"/>
-    <col width="17.6" customWidth="1" min="4" max="4"/>
+    <col width="24.2" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -4522,7 +4802,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>보정 범위(0.58~0.82)</t>
+          <t>보정 범위(k 0.5815~0.8169)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -4719,7 +4999,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.8~46.2</t>
+          <t>32.9~46.2</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4775,7 +5055,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.2~46.7</t>
+          <t>33.3~46.7</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -5370,6 +5650,656 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19.8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15.4" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15.4" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>혈위(경로)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>모형 원값</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>보정 평균</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>보정 하한</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>보정 상한</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>심장막 추정(−3~5mm)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>침체 50mm 대비</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>30mm 자입</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>40mm 자입</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>50mm 자입(침체 전장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CV17 (흉골공, 직자)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28~30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KI24-L (직자)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31~33</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PC1-L (안쪽 경사, 최단)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>35~37</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KI23-L (직자)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>35~37</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KI22-L (직자)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>35~37</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ST18-L (안쪽 경사, 최단)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>36~38</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KI24-R (최단)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>37~39</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ST16-L (직자)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>42~44</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KI23-R (최단)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D10" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>42~44</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CV15 (위로 45°)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>68</v>
+      </c>
+      <c r="C11" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>43~45</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CV15 (위로 30°)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>43~45</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CV14 (위로 60°)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>52~54</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>114%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CV14 (위로 45°)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>56~58</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>122%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5429,7 +6359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5623,7 +6553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5942,7 +6872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6976,271 +7906,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13.2" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9.9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>혈위</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ARI-Core A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ARI-Core B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>평균 ± 반범위</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>등급</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>게이트</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>등가중치(평균)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>민감도</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CV17</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C2" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>78.75 ± 1.25</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3 ⚠</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KI23-L</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="C3" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>75.0 ± 1.25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3 ⚠</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KI22-L</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="C4" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>72.5 ± 1.25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3 ⚠</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>가중치 민감(C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ST18-L</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="C5" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>71.25 ± 2.5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3 ⚠</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CV15</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="C6" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>70.0 ± 1.25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3 ⚠</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>가중치 민감(C)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>